--- a/job_application_forms/025_e_commerce_customer_service_job_application--job_application_forms.xlsx
+++ b/job_application_forms/025_e_commerce_customer_service_job_application--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'0_-_20,000',_'label':_'0_-_20,000'}</t>
+          <t>0_-_20,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '0 - 20,000', 'label': '0 - 20,000'}</t>
+          <t>0 - 20,000</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'20,001_-_40,000',_'label':_'20,001_-_40,000'}</t>
+          <t>20,001_-_40,000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '20,001 - 40,000', 'label': '20,001 - 40,000'}</t>
+          <t>20,001 - 40,000</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'40,001_-_60,000',_'label':_'40,001_-_60,000'}</t>
+          <t>40,001_-_60,000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '40,001 - 60,000', 'label': '40,001 - 60,000'}</t>
+          <t>40,001 - 60,000</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'60,001_-_80,000',_'label':_'60,001_-_80,000'}</t>
+          <t>60,001_-_80,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '60,001 - 80,000', 'label': '60,001 - 80,000'}</t>
+          <t>60,001 - 80,000</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High School', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_"bachelor's_degree",_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': "Bachelor's Degree", 'label': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_"master's_degree",_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': "Master's Degree", 'label': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
